--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0003T0006Z000C1N26_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0003T0006Z000C1N26_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>64.23011893565968</v>
+        <v>10.4373943270447</v>
       </c>
       <c r="D2" t="n">
-        <v>64.81042914115257</v>
+        <v>10.53169473543729</v>
       </c>
       <c r="E2" t="n">
-        <v>15.0500921152563</v>
+        <v>2.445639968729149</v>
       </c>
       <c r="F2" t="n">
-        <v>15.00918627464578</v>
+        <v>2.43899276962994</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>56.34326518498514</v>
+        <v>9.155780592560086</v>
       </c>
       <c r="D3" t="n">
-        <v>56.92240654917142</v>
+        <v>9.249891064240357</v>
       </c>
       <c r="E3" t="n">
-        <v>15.0500921152563</v>
+        <v>2.445639968729149</v>
       </c>
       <c r="F3" t="n">
-        <v>15.00918627464578</v>
+        <v>2.43899276962994</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>52.81791873713776</v>
+        <v>8.582911794784886</v>
       </c>
       <c r="D4" t="n">
-        <v>53.45857944799972</v>
+        <v>8.687019160299956</v>
       </c>
       <c r="E4" t="n">
-        <v>15.0500921152563</v>
+        <v>2.445639968729149</v>
       </c>
       <c r="F4" t="n">
-        <v>15.00918627464578</v>
+        <v>2.43899276962994</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>49.65963586462036</v>
+        <v>8.069690828000809</v>
       </c>
       <c r="D5" t="n">
-        <v>50.28368587476903</v>
+        <v>8.171098954649969</v>
       </c>
       <c r="E5" t="n">
-        <v>15.0500921152563</v>
+        <v>2.445639968729149</v>
       </c>
       <c r="F5" t="n">
-        <v>15.00918627464578</v>
+        <v>2.43899276962994</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>59.71597967626075</v>
+        <v>9.703846697392372</v>
       </c>
       <c r="D6" t="n">
-        <v>60.27174337604515</v>
+        <v>9.794158298607337</v>
       </c>
       <c r="E6" t="n">
-        <v>15.0500921152563</v>
+        <v>2.445639968729149</v>
       </c>
       <c r="F6" t="n">
-        <v>15.00918627464578</v>
+        <v>2.43899276962994</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>38.82594316903316</v>
+        <v>6.309215764967889</v>
       </c>
       <c r="D7" t="n">
-        <v>39.50989248194822</v>
+        <v>6.420357528316586</v>
       </c>
       <c r="E7" t="n">
-        <v>15.0500921152563</v>
+        <v>2.445639968729149</v>
       </c>
       <c r="F7" t="n">
-        <v>15.00918627464578</v>
+        <v>2.43899276962994</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>49.89618203290189</v>
+        <v>8.108129580346558</v>
       </c>
       <c r="D8" t="n">
-        <v>50.37545996323911</v>
+        <v>8.186012244026356</v>
       </c>
       <c r="E8" t="n">
-        <v>15.0500921152563</v>
+        <v>2.445639968729149</v>
       </c>
       <c r="F8" t="n">
-        <v>15.00918627464578</v>
+        <v>2.43899276962994</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>63.59281446520836</v>
+        <v>10.33383235059636</v>
       </c>
       <c r="D9" t="n">
-        <v>63.92850696311673</v>
+        <v>10.38838238150647</v>
       </c>
       <c r="E9" t="n">
-        <v>15.0500921152563</v>
+        <v>2.445639968729149</v>
       </c>
       <c r="F9" t="n">
-        <v>15.00918627464578</v>
+        <v>2.43899276962994</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>27.96372618399186</v>
+        <v>4.544105504898678</v>
       </c>
       <c r="D10" t="n">
-        <v>28.59676656401248</v>
+        <v>4.646974566652028</v>
       </c>
       <c r="E10" t="n">
-        <v>15.0500921152563</v>
+        <v>2.445639968729149</v>
       </c>
       <c r="F10" t="n">
-        <v>15.00918627464578</v>
+        <v>2.43899276962994</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>43.62247103501815</v>
+        <v>7.08865154319045</v>
       </c>
       <c r="D11" t="n">
-        <v>43.94706409028938</v>
+        <v>7.141397914672025</v>
       </c>
       <c r="E11" t="n">
-        <v>15.0500921152563</v>
+        <v>2.445639968729149</v>
       </c>
       <c r="F11" t="n">
-        <v>15.00918627464578</v>
+        <v>2.43899276962994</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>48.73878258231958</v>
+        <v>7.920052169626932</v>
       </c>
       <c r="D12" t="n">
-        <v>49.06443375868563</v>
+        <v>7.972970485786416</v>
       </c>
       <c r="E12" t="n">
-        <v>15.0500921152563</v>
+        <v>2.445639968729149</v>
       </c>
       <c r="F12" t="n">
-        <v>15.00918627464578</v>
+        <v>2.43899276962994</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>7.836601676518056</v>
+        <v>1.273447772434184</v>
       </c>
       <c r="D13" t="n">
-        <v>8.522357858853102</v>
+        <v>1.384883152063629</v>
       </c>
       <c r="E13" t="n">
-        <v>15.0500921152563</v>
+        <v>2.445639968729149</v>
       </c>
       <c r="F13" t="n">
-        <v>15.00918627464578</v>
+        <v>2.43899276962994</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>63.06225190855251</v>
+        <v>10.24761593513978</v>
       </c>
       <c r="D14" t="n">
-        <v>63.10189758209661</v>
+        <v>10.2540583570907</v>
       </c>
       <c r="E14" t="n">
-        <v>15.0500921152563</v>
+        <v>2.445639968729149</v>
       </c>
       <c r="F14" t="n">
-        <v>15.00918627464578</v>
+        <v>2.43899276962994</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>53.21864349729812</v>
+        <v>8.648029568310946</v>
       </c>
       <c r="D15" t="n">
-        <v>53.21584666909277</v>
+        <v>8.647575083727576</v>
       </c>
       <c r="E15" t="n">
-        <v>15.0500921152563</v>
+        <v>2.445639968729149</v>
       </c>
       <c r="F15" t="n">
-        <v>15.00918627464578</v>
+        <v>2.43899276962994</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>69.70929195728654</v>
+        <v>11.32775994305906</v>
       </c>
       <c r="D16" t="n">
-        <v>69.65811009665195</v>
+        <v>11.31944289070594</v>
       </c>
       <c r="E16" t="n">
-        <v>15.0500921152563</v>
+        <v>2.445639968729149</v>
       </c>
       <c r="F16" t="n">
-        <v>15.00918627464578</v>
+        <v>2.43899276962994</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>26.95480625390293</v>
+        <v>4.380156016259227</v>
       </c>
       <c r="D17" t="n">
-        <v>26.87657894887331</v>
+        <v>4.367444079191912</v>
       </c>
       <c r="E17" t="n">
-        <v>15.0500921152563</v>
+        <v>2.445639968729149</v>
       </c>
       <c r="F17" t="n">
-        <v>15.00918627464578</v>
+        <v>2.43899276962994</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>29.93607265215361</v>
+        <v>4.864611805974961</v>
       </c>
       <c r="D18" t="n">
-        <v>29.54497170432093</v>
+        <v>4.80105790195215</v>
       </c>
       <c r="E18" t="n">
-        <v>15.0500921152563</v>
+        <v>2.445639968729149</v>
       </c>
       <c r="F18" t="n">
-        <v>15.00918627464578</v>
+        <v>2.43899276962994</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>41.82980475895233</v>
+        <v>6.797343273329755</v>
       </c>
       <c r="D19" t="n">
-        <v>41.15062123946839</v>
+        <v>6.686975951413613</v>
       </c>
       <c r="E19" t="n">
-        <v>15.0500921152563</v>
+        <v>2.445639968729149</v>
       </c>
       <c r="F19" t="n">
-        <v>15.00918627464578</v>
+        <v>2.43899276962994</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>53.98104418480649</v>
+        <v>8.771919680031054</v>
       </c>
       <c r="D20" t="n">
-        <v>53.29536808009662</v>
+        <v>8.660497313015702</v>
       </c>
       <c r="E20" t="n">
-        <v>15.0500921152563</v>
+        <v>2.445639968729149</v>
       </c>
       <c r="F20" t="n">
-        <v>15.00918627464578</v>
+        <v>2.43899276962994</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>58.01223670321128</v>
+        <v>9.426988464271833</v>
       </c>
       <c r="D21" t="n">
-        <v>57.40334697692017</v>
+        <v>9.328043883749528</v>
       </c>
       <c r="E21" t="n">
-        <v>15.0500921152563</v>
+        <v>2.445639968729149</v>
       </c>
       <c r="F21" t="n">
-        <v>15.00918627464578</v>
+        <v>2.43899276962994</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
